--- a/consulting_forms/029_fashion_consultation_form--consulting_forms.xlsx
+++ b/consulting_forms/029_fashion_consultation_form--consulting_forms.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -895,8 +895,8 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="34" customWidth="1" min="1" max="1"/>
-    <col width="50" customWidth="1" min="2" max="2"/>
-    <col width="50" customWidth="1" min="3" max="3"/>
+    <col width="29" customWidth="1" min="2" max="2"/>
+    <col width="29" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -924,12 +924,12 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>{'value':_'wardrobe',_'label':_'wardrobe'}</t>
+          <t>wardrobe</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>{'value': 'Wardrobe', 'label': 'Wardrobe'}</t>
+          <t>Wardrobe</t>
         </is>
       </c>
     </row>
@@ -941,12 +941,12 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>{'value':_'styling',_'label':_'styling'}</t>
+          <t>styling</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>{'value': 'Styling', 'label': 'Styling'}</t>
+          <t>Styling</t>
         </is>
       </c>
     </row>
@@ -958,12 +958,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>{'value':_'personalized_fashion_advice',_'label':_'personalized_fashion_advice'}</t>
+          <t>personalized_fashion_advice</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>{'value': 'Personalized Fashion Advice', 'label': 'Personalized Fashion Advice'}</t>
+          <t>Personalized Fashion Advice</t>
         </is>
       </c>
     </row>
@@ -975,12 +975,12 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>{'value':_'other',_'label':_'other'}</t>
+          <t>other</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>{'value': 'Other', 'label': 'Other'}</t>
+          <t>Other</t>
         </is>
       </c>
     </row>
@@ -992,12 +992,12 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>{'value':_'fashionable',_'label':_'fashionable'}</t>
+          <t>fashionable</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>{'value': 'Fashionable', 'label': 'Fashionable'}</t>
+          <t>Fashionable</t>
         </is>
       </c>
     </row>
@@ -1009,12 +1009,12 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>{'value':_'elegant',_'label':_'elegant'}</t>
+          <t>elegant</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>{'value': 'Elegant', 'label': 'Elegant'}</t>
+          <t>Elegant</t>
         </is>
       </c>
     </row>
@@ -1026,12 +1026,12 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>{'value':_'trendy',_'label':_'trendy'}</t>
+          <t>trendy</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>{'value': 'Trendy', 'label': 'Trendy'}</t>
+          <t>Trendy</t>
         </is>
       </c>
     </row>
@@ -1043,12 +1043,12 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>{'value':_'classic',_'label':_'classic'}</t>
+          <t>classic</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>{'value': 'Classic', 'label': 'Classic'}</t>
+          <t>Classic</t>
         </is>
       </c>
     </row>
@@ -1060,12 +1060,12 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>{'value':_'quirky',_'label':_'quirky'}</t>
+          <t>quirky</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>{'value': 'Quirky', 'label': 'Quirky'}</t>
+          <t>Quirky</t>
         </is>
       </c>
     </row>
@@ -1077,12 +1077,12 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>{'value':_'other',_'label':_'other'}</t>
+          <t>other</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>{'value': 'Other', 'label': 'Other'}</t>
+          <t>Other</t>
         </is>
       </c>
     </row>
@@ -1094,12 +1094,12 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>{'value':_'black',_'label':_'black'}</t>
+          <t>black</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>{'value': 'Black', 'label': 'Black'}</t>
+          <t>Black</t>
         </is>
       </c>
     </row>
@@ -1111,12 +1111,12 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>{'value':_'white',_'label':_'white'}</t>
+          <t>white</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>{'value': 'White', 'label': 'White'}</t>
+          <t>White</t>
         </is>
       </c>
     </row>
@@ -1128,12 +1128,12 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>{'value':_'red',_'label':_'red'}</t>
+          <t>red</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>{'value': 'Red', 'label': 'Red'}</t>
+          <t>Red</t>
         </is>
       </c>
     </row>
@@ -1145,12 +1145,12 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>{'value':_'blue',_'label':_'blue'}</t>
+          <t>blue</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>{'value': 'Blue', 'label': 'Blue'}</t>
+          <t>Blue</t>
         </is>
       </c>
     </row>
@@ -1162,12 +1162,12 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>{'value':_'green',_'label':_'green'}</t>
+          <t>green</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>{'value': 'Green', 'label': 'Green'}</t>
+          <t>Green</t>
         </is>
       </c>
     </row>
@@ -1179,12 +1179,12 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>{'value':_'yellow',_'label':_'yellow'}</t>
+          <t>yellow</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>{'value': 'Yellow', 'label': 'Yellow'}</t>
+          <t>Yellow</t>
         </is>
       </c>
     </row>
@@ -1196,12 +1196,12 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>{'value':_'other',_'label':_'other'}</t>
+          <t>other</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>{'value': 'Other', 'label': 'Other'}</t>
+          <t>Other</t>
         </is>
       </c>
     </row>
@@ -1213,12 +1213,12 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>{'value':_'2-4',_'label':_'2-4'}</t>
+          <t>2-4</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>{'value': '2-4', 'label': '2-4'}</t>
+          <t>2-4</t>
         </is>
       </c>
     </row>
@@ -1230,12 +1230,12 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>{'value':_'6-8',_'label':_'6-8'}</t>
+          <t>6-8</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>{'value': '6-8', 'label': '6-8'}</t>
+          <t>6-8</t>
         </is>
       </c>
     </row>
@@ -1247,12 +1247,12 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>{'value':_'10-12',_'label':_'10-12'}</t>
+          <t>10-12</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>{'value': '10-12', 'label': '10-12'}</t>
+          <t>10-12</t>
         </is>
       </c>
     </row>
@@ -1264,12 +1264,12 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>{'value':_'14-16',_'label':_'14-16'}</t>
+          <t>14-16</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>{'value': '14-16', 'label': '14-16'}</t>
+          <t>14-16</t>
         </is>
       </c>
     </row>
@@ -1281,12 +1281,12 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>{'value':_'other',_'label':_'other'}</t>
+          <t>other</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>{'value': 'Other', 'label': 'Other'}</t>
+          <t>Other</t>
         </is>
       </c>
     </row>
@@ -1298,12 +1298,12 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>{'value':_'monday',_'label':_'monday'}</t>
+          <t>monday</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>{'value': 'Monday', 'label': 'Monday'}</t>
+          <t>Monday</t>
         </is>
       </c>
     </row>
@@ -1315,12 +1315,12 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>{'value':_'tuesday',_'label':_'tuesday'}</t>
+          <t>tuesday</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>{'value': 'Tuesday', 'label': 'Tuesday'}</t>
+          <t>Tuesday</t>
         </is>
       </c>
     </row>
@@ -1332,12 +1332,12 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>{'value':_'wednesday',_'label':_'wednesday'}</t>
+          <t>wednesday</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>{'value': 'Wednesday', 'label': 'Wednesday'}</t>
+          <t>Wednesday</t>
         </is>
       </c>
     </row>
@@ -1349,12 +1349,12 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>{'value':_'thursday',_'label':_'thursday'}</t>
+          <t>thursday</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>{'value': 'Thursday', 'label': 'Thursday'}</t>
+          <t>Thursday</t>
         </is>
       </c>
     </row>
@@ -1366,12 +1366,12 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>{'value':_'friday',_'label':_'friday'}</t>
+          <t>friday</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>{'value': 'Friday', 'label': 'Friday'}</t>
+          <t>Friday</t>
         </is>
       </c>
     </row>
@@ -1383,12 +1383,12 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>{'value':_'saturday',_'label':_'saturday'}</t>
+          <t>saturday</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>{'value': 'Saturday', 'label': 'Saturday'}</t>
+          <t>Saturday</t>
         </is>
       </c>
     </row>
@@ -1400,12 +1400,12 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>{'value':_'sunday',_'label':_'sunday'}</t>
+          <t>sunday</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>{'value': 'Sunday', 'label': 'Sunday'}</t>
+          <t>Sunday</t>
         </is>
       </c>
     </row>
@@ -1417,12 +1417,12 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>{'value':_'phone',_'label':_'phone'}</t>
+          <t>phone</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>{'value': 'Phone', 'label': 'Phone'}</t>
+          <t>Phone</t>
         </is>
       </c>
     </row>
@@ -1434,12 +1434,12 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>{'value':_'email',_'label':_'email'}</t>
+          <t>email</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>{'value': 'Email', 'label': 'Email'}</t>
+          <t>Email</t>
         </is>
       </c>
     </row>
@@ -1451,12 +1451,12 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>{'value':_'mail',_'label':_'mail'}</t>
+          <t>mail</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>{'value': 'Mail', 'label': 'Mail'}</t>
+          <t>Mail</t>
         </is>
       </c>
     </row>
@@ -1468,12 +1468,12 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>{'value':_'other',_'label':_'other'}</t>
+          <t>other</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>{'value': 'Other', 'label': 'Other'}</t>
+          <t>Other</t>
         </is>
       </c>
     </row>
